--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-cleaning-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-cleaning-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Outliers không phải lúc nào cũng là lỗi nhập liệu. Trong phân tích gian lận (Fraud Detection), chính các giao dịch Outlier (số tiền giao dịch cực lớn, vị trí địa lý bất thường) là tiêu điểm cần tìm kiếm. DA phải phân tích nguồn gốc của Outlier trước khi quyết định xử lý.</v>
       </c>
       <c r="F2" t="str">
+        <v>Vì Outlier là các giá trị bắt buộc phải có để tính toán hệ số tương quan của mô hình hồi quy — yêu cầu thống kê</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Vì khách hàng sẽ khiếu nại nếu họ phát hiện ra tài khoản của họ bị hệ thống đánh dấu là Outlier — khiếu nại khách hàng</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Vì việc xóa Outlier sẽ tự động làm hỏng cấu trúc logic của cơ sở dữ liệu quan hệ — hỏng database</v>
+      </c>
+      <c r="I2" t="str">
         <v>Vì Outlier có thể chứa đựng những thông tin thực tế quan trọng (như giao dịch gian lận tài chính, sự cố hệ thống); xóa bỏ sẽ làm mất đi các insight dị biệt này — Outlier mang giá trị thông tin đặc biệt</v>
       </c>
-      <c r="G2" t="str">
-        <v>Vì việc xóa Outlier sẽ tự động làm hỏng cấu trúc logic của cơ sở dữ liệu quan hệ — hỏng database</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Vì Outlier là các giá trị bắt buộc phải có để tính toán hệ số tương quan của mô hình hồi quy — yêu cầu thống kê</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Vì khách hàng sẽ khiếu nại nếu họ phát hiện ra tài khoản của họ bị hệ thống đánh dấu là Outlier — khiếu nại khách hàng</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>MICE là kỹ thuật điền khuyết tiên tiến. Thay vì chỉ tính trung bình đơn giản trên 1 cột (Univariate), MICE xem xét giá trị của các cột khác để dự báo giá trị khuyết thiếu một cách khoa học, giữ lại phân phối tự nhiên của dữ liệu.</v>
       </c>
       <c r="F3" t="str">
-        <v>MICE ước tính giá trị bị khuyết của một biến dựa trên các mối quan hệ tương quan với các biến khác trong bộ dữ liệu thông qua mô hình dự báo hồi quy lặp đi lặp lại — điền khuyết đa biến đệ quy</v>
+        <v>MICE gửi yêu cầu API tự động sang hệ thống bên thứ ba để xin lại dữ liệu bị mất — tích hợp API lấy lại dữ liệu</v>
       </c>
       <c r="G3" t="str">
         <v>MICE điền nhanh số 0 hoặc giá trị trung vị vào tất cả các ô bị trống một cách ngẫu nhiên — điền giá trị đơn giản</v>
       </c>
       <c r="H3" t="str">
-        <v>MICE gửi yêu cầu API tự động sang hệ thống bên thứ ba để xin lại dữ liệu bị mất — tích hợp API lấy lại dữ liệu</v>
+        <v>MICE sử dụng trí tuệ nhân tạo AI để tự vẽ lại hình ảnh chân dung của khách hàng bị thiếu — vẽ ảnh thiếu</v>
       </c>
       <c r="I3" t="str">
-        <v>MICE sử dụng trí tuệ nhân tạo AI để tự vẽ lại hình ảnh chân dung của khách hàng bị thiếu — vẽ ảnh thiếu</v>
+        <v>MICE ước tính giá trị bị khuyết của một biến dựa trên các mối quan hệ tương quan với các biến khác trong bộ dữ liệu thông qua mô hình dự báo hồi quy lặp đi lặp lại — điền khuyết đa biến đệ quy</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Hàm `pd.to_datetime()` của Pandas cực kỳ mạnh mẽ, nó có thể tự động nhận diện và chuyển đổi nhiều định dạng ngày tháng khác nhau về kiểu dữ liệu `datetime64[ns]` chuẩn. Tham số `errors='coerce'` giúp chuyển các dòng bị lỗi cú pháp nặng (không thể parse) thành NaT (Not a Time) thay vì làm sập chương trình.</v>
       </c>
       <c r="F4" t="str">
+        <v>Viết các câu lệnh chuỗi cắt ghép bằng hàm `.split()` dựa trên ký tự gạch chéo để trích xuất ngày, tháng, năm — cắt ghép chuỗi thủ công</v>
+      </c>
+      <c r="G4" t="str">
         <v>Sử dụng hàm `pd.to_datetime(column, errors='coerce')` để Pandas tự động phân tích cú pháp và chuyển đổi về định dạng chuẩn — tự động parse datetime</v>
       </c>
-      <c r="G4" t="str">
-        <v>Viết các câu lệnh chuỗi cắt ghép bằng hàm `.split()` dựa trên ký tự gạch chéo để trích xuất ngày, tháng, năm — cắt ghép chuỗi thủ công</v>
-      </c>
       <c r="H4" t="str">
+        <v>Yêu cầu lập trình viên Frontend khóa tính năng chọn ngày trên giao diện của trang web — khóa giao diện</v>
+      </c>
+      <c r="I4" t="str">
         <v>Xóa bỏ toàn bộ các dòng có định dạng ngày tháng không khớp với dòng đầu tiên của bảng — xóa dòng định dạng lệch</v>
       </c>
-      <c r="I4" t="str">
-        <v>Yêu cầu lập trình viên Frontend khóa tính năng chọn ngày trên giao diện của trang web — khóa giao diện</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
         <v>Quy tắc IQR định nghĩa: $IQR = Q_3 - Q_1$. Ranh giới dưới là $Q_1 - 1.5 \cdot IQR$, ranh giới trên là $Q_3 + 1.5 \cdot IQR$. Bất kỳ điểm dữ liệu nào nằm ngoài khoảng ranh giới này đều được thuật toán của Box Plot đánh dấu là Outlier.</v>
       </c>
       <c r="F5" t="str">
+        <v>Các điểm dữ liệu nằm bên trong khu vực hộp giữa phân vị 25 ($Q_1$) và phân vị 75 ($Q_3$) — vùng hộp trung tâm</v>
+      </c>
+      <c r="G5" t="str">
         <v>Các điểm nằm ngoài khoảng từ $Q_1 - 1.5 \cdot IQR$ đến $Q_3 + 1.5 \cdot IQR$ — ranh giới IQR</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Các điểm dữ liệu nằm bên trong khu vực hộp giữa phân vị 25 ($Q_1$) và phân vị 75 ($Q_3$) — vùng hộp trung tâm</v>
       </c>
       <c r="H5" t="str">
         <v>Các điểm dữ liệu có giá trị lớn hơn giá trị trung bình cộng của bộ mẫu dữ liệu — lớn hơn trung bình</v>
@@ -568,7 +568,7 @@
         <v>Các điểm dữ liệu có tần suất xuất hiện trùng lặp nhiều nhất trong bảng — tần suất trùng lặp cao</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Lệch chuẩn dữ liệu chữ (Text inconsistency) do thiếu ràng buộc nhập liệu. BA/DA phải thiết lập bảng ánh xạ (ví dụ: {"nam": "Nam", "M": "Nam", "nu": "Nữ", "F": "Nữ"}) để đưa dữ liệu phân loại về định dạng nhất quán trước khi phân tích nhóm.</v>
       </c>
       <c r="F6" t="str">
+        <v>Thay thế tất cả các giá trị giới tính bằng giá trị xuất hiện nhiều nhất (mode) mà không cần phân loại — điền mode cưỡng bức</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Tự động đổi tất cả các giá trị giới tính sang dạng số nguyên tự tăng bắt đầu từ số 1 — số hóa tự tăng</v>
+      </c>
+      <c r="H6" t="str">
         <v>Ánh xạ (Mapping) chuyển đổi tất cả về một bộ giá trị chuẩn thống nhất (ví dụ: `Nam` / `Nữ` hoặc `M` / `F`), và xử lý các giá trị trống (NULL) theo quy tắc nghiệp vụ — chuẩn hóa ánh xạ dữ liệu phân loại</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>Xóa bỏ toàn bộ các dòng chứa giá trị `M` và `F` vì chúng là ký tự tiếng Anh không phù hợp — xóa bỏ dòng tiếng Anh</v>
       </c>
-      <c r="H6" t="str">
-        <v>Thay thế tất cả các giá trị giới tính bằng giá trị xuất hiện nhiều nhất (mode) mà không cần phân loại — điền mode cưỡng bức</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Tự động đổi tất cả các giá trị giới tính sang dạng số nguyên tự tăng bắt đầu từ số 1 — số hóa tự tăng</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -626,10 +626,10 @@
         <v>Xóa bỏ hoàn toàn các dòng dữ liệu chứa Outliers khỏi DataFrame — xóa dòng ngoại lai</v>
       </c>
       <c r="H7" t="str">
+        <v>Chuyển đổi toàn bộ Outliers thành giá trị NULL để thuật toán tự động bỏ qua khi chạy — chuyển thành NULL</v>
+      </c>
+      <c r="I7" t="str">
         <v>Cộng thêm một hằng số cố định vào tất cả các Outliers để đưa chúng về gần giá trị trung bình — cộng hằng số hiệu chỉnh</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Chuyển đổi toàn bộ Outliers thành giá trị NULL để thuật toán tự động bỏ qua khi chạy — chuyển thành NULL</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -652,19 +652,19 @@
         <v>MCAR là trường hợp lý tưởng (ví dụ: đánh rơi tệp khảo sát ngẫu nhiên). MNAR là trường hợp phức tạp (ví dụ: người có thu nhập rất cao thường từ chối khai báo thu nhập trong khảo sát, làm biến thu nhập bị khuyết phụ thuộc vào giá trị thu nhập thực tế). Xử lý MNAR đòi hỏi mô hình hóa phức tạp hơn.</v>
       </c>
       <c r="F8" t="str">
+        <v>MCAR do lỗi lập trình viên viết code sai; MNAR do máy chủ bị mất kết nối mạng internet — nguyên nhân kỹ thuật</v>
+      </c>
+      <c r="G8" t="str">
+        <v>MCAR có thể tự động sửa lỗi; MNAR bắt buộc phải xóa bỏ bảng dữ liệu đó đi — khả năng sửa lỗi</v>
+      </c>
+      <c r="H8" t="str">
+        <v>MCAR chỉ xảy ra ở dữ liệu số; MNAR chỉ xảy ra ở dữ liệu chuỗi văn bản chữ — kiểu dữ liệu bị khuyết</v>
+      </c>
+      <c r="I8" t="str">
         <v>MCAR: Dữ liệu khuyết thiếu hoàn toàn ngẫu nhiên không phụ thuộc vào bất kỳ biến nào; MNAR: Dữ liệu khuyết thiếu có chủ đích, phụ thuộc trực tiếp vào chính giá trị của biến bị thiếu đó — ngẫu nhiên khách quan vs chủ quan hệ thống</v>
       </c>
-      <c r="G8" t="str">
-        <v>MCAR chỉ xảy ra ở dữ liệu số; MNAR chỉ xảy ra ở dữ liệu chuỗi văn bản chữ — kiểu dữ liệu bị khuyết</v>
-      </c>
-      <c r="H8" t="str">
-        <v>MCAR do lỗi lập trình viên viết code sai; MNAR do máy chủ bị mất kết nối mạng internet — nguyên nhân kỹ thuật</v>
-      </c>
-      <c r="I8" t="str">
-        <v>MCAR có thể tự động sửa lỗi; MNAR bắt buộc phải xóa bỏ bảng dữ liệu đó đi — khả năng sửa lỗi</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -687,10 +687,10 @@
         <v>Min-Max đưa dữ liệu về khoảng cố định [0, 1]; Standardization đưa dữ liệu về phân phối có trung bình bằng 0 và độ lệch chuẩn bằng 1 — [0, 1] vs Phân phối chuẩn</v>
       </c>
       <c r="G9" t="str">
+        <v>Min-Max do BA tự tính tay; Standardization bắt buộc phải chạy bằng thư viện Python — phân vai trò tính toán</v>
+      </c>
+      <c r="H9" t="str">
         <v>Min-Max chỉ áp dụng cho số nguyên dương; Standardization chỉ áp dụng cho số nguyên âm — giới hạn miền số</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Min-Max do BA tự tính tay; Standardization bắt buộc phải chạy bằng thư viện Python — phân vai trò tính toán</v>
       </c>
       <c r="I9" t="str">
         <v>Min-Max làm tăng kích thước tệp tin dữ liệu; Standardization làm giảm dung lượng tệp tin — tác động bộ nhớ</v>
@@ -716,19 +716,19 @@
         <v>Nội suy (Interpolation) là kỹ thuật điền khuyết đắc lực cho chuỗi thời gian (ví dụ: nhiệt độ đo theo giờ bị mất dữ liệu lúc 10h, hệ thống sẽ lấy trung bình giữa 9h và 11h để điền vào, giúp giữ tính liên tục của biểu đồ).</v>
       </c>
       <c r="F10" t="str">
-        <v>Ước tính giá trị khuyết bằng phép nội suy tuyến tính dựa trên các giá trị của các bản ghi liền trước và liền sau (thích hợp cho dữ liệu chuỗi thời gian - Time Series) — nội suy tuyến tính chuỗi thời gian</v>
+        <v>Xóa bỏ toàn bộ các dòng chứa giá trị khuyết thiếu khỏi DataFrame — xóa dòng chứa khuyết</v>
       </c>
       <c r="G10" t="str">
         <v>Thay thế giá trị khuyết bằng giá trị trung bình của toàn bộ cột dữ liệu đó — điền giá trị trung bình</v>
       </c>
       <c r="H10" t="str">
-        <v>Xóa bỏ toàn bộ các dòng chứa giá trị khuyết thiếu khỏi DataFrame — xóa dòng chứa khuyết</v>
+        <v>Ước tính giá trị khuyết bằng phép nội suy tuyến tính dựa trên các giá trị của các bản ghi liền trước và liền sau (thích hợp cho dữ liệu chuỗi thời gian - Time Series) — nội suy tuyến tính chuỗi thời gian</v>
       </c>
       <c r="I10" t="str">
         <v>Tự động gọi API để cập nhật lại dữ liệu từ hệ thống nguồn — cập nhật dữ liệu tự động</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -751,13 +751,13 @@
         <v>Sử dụng thuật toán so khớp chuỗi mờ (Fuzzy String Matching - như độ đo Levenshtein Distance) để tính toán độ tương đồng và gom nhóm về một tên chuẩn — so khớp chuỗi mờ</v>
       </c>
       <c r="G11" t="str">
+        <v>Xóa bỏ toàn bộ phần thông tin tỉnh thành và chỉ giữ lại tên số nhà, tên đường — loại bỏ tỉnh thành</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Yêu cầu lập trình viên Frontend xóa bỏ ô nhập địa chỉ tự do và thay bằng 3 ô chọn Select Box (Tỉnh/Huyện/Xã) cấp quận huyện — giải pháp chặn lỗi từ nguồn</v>
+      </c>
+      <c r="I11" t="str">
         <v>Viết các câu lệnh điều kiện IF-ELSE cứng nhắc cho tất cả các trường hợp có thể xảy ra trên đời — IF-ELSE cứng nhắc thủ công</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Xóa bỏ toàn bộ phần thông tin tỉnh thành và chỉ giữ lại tên số nhà, tên đường — loại bỏ tỉnh thành</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Yêu cầu lập trình viên Frontend xóa bỏ ô nhập địa chỉ tự do và thay bằng 3 ô chọn Select Box (Tỉnh/Huyện/Xã) cấp quận huyện — giải pháp chặn lỗi từ nguồn</v>
       </c>
       <c r="J11">
         <v>1</v>
